--- a/test-attachments/mm-switch-fabric.xlsx
+++ b/test-attachments/mm-switch-fabric.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Fabric Nodes" sheetId="1" r:id="rId1"/>
-    <sheet name="Compute Nodes" sheetId="2" r:id="rId2"/>
+    <sheet name="Compute Nodes" sheetId="1" r:id="rId1"/>
+    <sheet name="Fabric Switches" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,594 +398,572 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Node</v>
+        <v>Compute ID</v>
       </c>
       <c r="B1" t="str">
+        <v>OS</v>
+      </c>
+      <c r="C1" t="str">
         <v>Role</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Ports</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>spine-1</v>
+        <v>comp-fabric-1</v>
       </c>
       <c r="B2" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C2" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>spine-2</v>
+        <v>comp-fabric-2</v>
       </c>
       <c r="B3" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C3" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>spine-3</v>
+        <v>comp-fabric-3</v>
       </c>
       <c r="B4" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C4" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>spine-4</v>
+        <v>comp-fabric-4</v>
       </c>
       <c r="B5" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C5" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>spine-5</v>
+        <v>comp-fabric-5</v>
       </c>
       <c r="B6" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C6" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>spine-6</v>
+        <v>comp-fabric-6</v>
       </c>
       <c r="B7" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C7" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>spine-7</v>
+        <v>comp-fabric-7</v>
       </c>
       <c r="B8" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C8" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>spine-8</v>
+        <v>comp-fabric-8</v>
       </c>
       <c r="B9" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C9" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>spine-9</v>
+        <v>comp-fabric-9</v>
       </c>
       <c r="B10" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C10" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>spine-10</v>
+        <v>comp-fabric-10</v>
       </c>
       <c r="B11" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C11" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>spine-11</v>
+        <v>comp-fabric-11</v>
       </c>
       <c r="B12" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C12" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>spine-12</v>
+        <v>comp-fabric-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C13" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>spine-13</v>
+        <v>comp-fabric-13</v>
       </c>
       <c r="B14" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C14" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>spine-14</v>
+        <v>comp-fabric-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C15" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>spine-15</v>
+        <v>comp-fabric-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C16" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>spine-16</v>
+        <v>comp-fabric-16</v>
       </c>
       <c r="B17" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C17" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>spine-17</v>
+        <v>comp-fabric-17</v>
       </c>
       <c r="B18" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C18" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>spine-18</v>
+        <v>comp-fabric-18</v>
       </c>
       <c r="B19" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C19" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>spine-19</v>
+        <v>comp-fabric-19</v>
       </c>
       <c r="B20" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C20" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>spine-20</v>
+        <v>comp-fabric-20</v>
       </c>
       <c r="B21" t="str">
-        <v>Network Switch</v>
+        <v>Debian 12</v>
       </c>
       <c r="C21" t="str">
-        <v>32x100G</v>
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>comp-fabric-21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>comp-fabric-22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>comp-fabric-23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>comp-fabric-24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>comp-fabric-25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>comp-fabric-26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>comp-fabric-27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>comp-fabric-28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>comp-fabric-29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Host Server</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>comp-fabric-30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Debian 12</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Host Server</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Server</v>
+        <v>Fabric Switch ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Type</v>
+        <v>Model</v>
       </c>
       <c r="C1" t="str">
-        <v>OS</v>
+        <v>Role</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>blade-1</v>
+        <v>fabric-spine-1</v>
       </c>
       <c r="B2" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C2" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>blade-2</v>
+        <v>fabric-spine-2</v>
       </c>
       <c r="B3" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C3" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>blade-3</v>
+        <v>fabric-spine-3</v>
       </c>
       <c r="B4" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C4" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>blade-4</v>
+        <v>fabric-spine-4</v>
       </c>
       <c r="B5" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C5" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>blade-5</v>
+        <v>fabric-spine-5</v>
       </c>
       <c r="B6" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C6" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>blade-6</v>
+        <v>fabric-spine-6</v>
       </c>
       <c r="B7" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C7" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>blade-7</v>
+        <v>fabric-spine-7</v>
       </c>
       <c r="B8" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C8" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>blade-8</v>
+        <v>fabric-spine-8</v>
       </c>
       <c r="B9" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C9" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>blade-9</v>
+        <v>fabric-spine-9</v>
       </c>
       <c r="B10" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C10" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>blade-10</v>
+        <v>fabric-spine-10</v>
       </c>
       <c r="B11" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C11" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>blade-11</v>
+        <v>fabric-spine-11</v>
       </c>
       <c r="B12" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C12" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>blade-12</v>
+        <v>fabric-spine-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C13" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>blade-13</v>
+        <v>fabric-spine-13</v>
       </c>
       <c r="B14" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C14" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>blade-14</v>
+        <v>fabric-spine-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C15" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>blade-15</v>
+        <v>fabric-spine-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C16" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>blade-16</v>
+        <v>fabric-spine-16</v>
       </c>
       <c r="B17" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C17" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>blade-17</v>
+        <v>fabric-spine-17</v>
       </c>
       <c r="B18" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C18" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>blade-18</v>
+        <v>fabric-spine-18</v>
       </c>
       <c r="B19" t="str">
-        <v>Host Server</v>
+        <v>Arista 7050</v>
       </c>
       <c r="C19" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>blade-19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C20" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>blade-20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C21" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>blade-21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C22" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>blade-22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C23" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>blade-23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C24" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>blade-24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C25" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>blade-25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C26" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>blade-26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C27" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>blade-27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C28" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>blade-28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C29" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>blade-29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C30" t="str">
-        <v>RHEL 9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>blade-30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Host Server</v>
-      </c>
-      <c r="C31" t="str">
-        <v>RHEL 9</v>
+        <v>Network Switch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>